--- a/artfynd/A 39958-2026 artfynd.xlsx
+++ b/artfynd/A 39958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938370</v>
       </c>
       <c r="B2" t="n">
-        <v>80592</v>
+        <v>80596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136938396</v>
       </c>
       <c r="B3" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136938517</v>
       </c>
       <c r="B4" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136938241</v>
       </c>
       <c r="B5" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39958-2026 artfynd.xlsx
+++ b/artfynd/A 39958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938370</v>
       </c>
       <c r="B2" t="n">
-        <v>80596</v>
+        <v>80598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136938396</v>
       </c>
       <c r="B3" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136938517</v>
       </c>
       <c r="B4" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136938241</v>
       </c>
       <c r="B5" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39958-2026 artfynd.xlsx
+++ b/artfynd/A 39958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938370</v>
       </c>
       <c r="B2" t="n">
-        <v>80598</v>
+        <v>80599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136938396</v>
       </c>
       <c r="B3" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136938517</v>
       </c>
       <c r="B4" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136938241</v>
       </c>
       <c r="B5" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39958-2026 artfynd.xlsx
+++ b/artfynd/A 39958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938370</v>
       </c>
       <c r="B2" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136938396</v>
       </c>
       <c r="B3" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136938517</v>
       </c>
       <c r="B4" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136938241</v>
       </c>
       <c r="B5" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39958-2026 artfynd.xlsx
+++ b/artfynd/A 39958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938370</v>
       </c>
       <c r="B2" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136938396</v>
       </c>
       <c r="B3" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136938517</v>
       </c>
       <c r="B4" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136938241</v>
       </c>
       <c r="B5" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39958-2026 artfynd.xlsx
+++ b/artfynd/A 39958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938370</v>
       </c>
       <c r="B2" t="n">
-        <v>80604</v>
+        <v>80617</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136938396</v>
       </c>
       <c r="B3" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136938517</v>
       </c>
       <c r="B4" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136938241</v>
       </c>
       <c r="B5" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39958-2026 artfynd.xlsx
+++ b/artfynd/A 39958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938370</v>
       </c>
       <c r="B2" t="n">
-        <v>80617</v>
+        <v>80619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136938396</v>
       </c>
       <c r="B3" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136938517</v>
       </c>
       <c r="B4" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136938241</v>
       </c>
       <c r="B5" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39958-2026 artfynd.xlsx
+++ b/artfynd/A 39958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938370</v>
       </c>
       <c r="B2" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136938396</v>
       </c>
       <c r="B3" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136938517</v>
       </c>
       <c r="B4" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136938241</v>
       </c>
       <c r="B5" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39958-2026 artfynd.xlsx
+++ b/artfynd/A 39958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938370</v>
       </c>
       <c r="B2" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136938396</v>
       </c>
       <c r="B3" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136938517</v>
       </c>
       <c r="B4" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136938241</v>
       </c>
       <c r="B5" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39958-2026 artfynd.xlsx
+++ b/artfynd/A 39958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938370</v>
       </c>
       <c r="B2" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136938396</v>
       </c>
       <c r="B3" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136938517</v>
       </c>
       <c r="B4" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136938241</v>
       </c>
       <c r="B5" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39958-2026 artfynd.xlsx
+++ b/artfynd/A 39958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938370</v>
       </c>
       <c r="B2" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136938396</v>
       </c>
       <c r="B3" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136938517</v>
       </c>
       <c r="B4" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136938241</v>
       </c>
       <c r="B5" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39958-2026 artfynd.xlsx
+++ b/artfynd/A 39958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938370</v>
       </c>
       <c r="B2" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136938396</v>
       </c>
       <c r="B3" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136938517</v>
       </c>
       <c r="B4" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136938241</v>
       </c>
       <c r="B5" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39958-2026 artfynd.xlsx
+++ b/artfynd/A 39958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938370</v>
       </c>
       <c r="B2" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136938396</v>
       </c>
       <c r="B3" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136938517</v>
       </c>
       <c r="B4" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136938241</v>
       </c>
       <c r="B5" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39958-2026 artfynd.xlsx
+++ b/artfynd/A 39958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938370</v>
       </c>
       <c r="B2" t="n">
-        <v>80651</v>
+        <v>80652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136938396</v>
       </c>
       <c r="B3" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136938517</v>
       </c>
       <c r="B4" t="n">
-        <v>80662</v>
+        <v>80663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136938241</v>
       </c>
       <c r="B5" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39958-2026 artfynd.xlsx
+++ b/artfynd/A 39958-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136938370</v>
       </c>
       <c r="B2" t="n">
-        <v>80652</v>
+        <v>80655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136938396</v>
       </c>
       <c r="B3" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136938517</v>
       </c>
       <c r="B4" t="n">
-        <v>80663</v>
+        <v>80666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136938241</v>
       </c>
       <c r="B5" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
